--- a/extra/report/No.課題3_テスト結果.xlsx
+++ b/extra/report/No.課題3_テスト結果.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395D0375-A472-40A8-85A2-4BCD684FC3A7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39829A62-F3B5-4A39-9925-342EA528E11B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -494,17 +494,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>137575</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>373411</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>34059</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6A51A69-D2F8-4250-B952-D500E201A7DB}"/>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA9608B5-6749-4C03-8FF4-E438E46DD3AB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -526,8 +526,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="857250"/>
-          <a:ext cx="10058400" cy="2023525"/>
+          <a:off x="687457" y="869674"/>
+          <a:ext cx="7935432" cy="3686689"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -538,16 +538,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>657225</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>371475</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>292790</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>46796</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>289892</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>8282</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -562,8 +562,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3400425" y="1819275"/>
-          <a:ext cx="400050" cy="266700"/>
+          <a:off x="980247" y="2655818"/>
+          <a:ext cx="684558" cy="483290"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -606,16 +606,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>171451</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>679173</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>57979</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>684973</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>157370</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -630,8 +630,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="3581400" y="2228850"/>
-          <a:ext cx="19051" cy="1104900"/>
+          <a:off x="1366630" y="3188805"/>
+          <a:ext cx="5800" cy="1664804"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -660,68 +660,18 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>658561</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>143326</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="図 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2DCF0F6-F5E1-44B6-BFA0-73B0F3F2F4B0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="3429000"/>
-          <a:ext cx="9573961" cy="3229426"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>671881</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>86458</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>424231</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>95983</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>564206</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>169285</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>316556</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>4875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -736,13 +686,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8936650" y="3119804"/>
-          <a:ext cx="2507273" cy="515083"/>
+          <a:off x="6751315" y="4865524"/>
+          <a:ext cx="2502176" cy="531329"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -32522"/>
-            <a:gd name="adj2" fmla="val 102329"/>
+            <a:gd name="adj1" fmla="val -60989"/>
+            <a:gd name="adj2" fmla="val 32181"/>
           </a:avLst>
         </a:prstGeom>
       </xdr:spPr>
@@ -798,6 +748,56 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>206619</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>113048</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1CDDD29-7E1E-4C86-AFD0-B452B01FB085}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="687457" y="5044109"/>
+          <a:ext cx="5706271" cy="2896004"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -806,22 +806,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>10026</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>158519</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>135978</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>71647</xdr:rowOff>
+      <xdr:colOff>23812</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>5953</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>272414</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>61163</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F289F08-2175-43F7-BBDE-B62B4DC36BB4}"/>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4E1A75D-6910-4543-9231-668AAE39E285}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -843,8 +843,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="285750" y="1010756"/>
-          <a:ext cx="10052004" cy="1788049"/>
+          <a:off x="297656" y="1041797"/>
+          <a:ext cx="6820852" cy="3162741"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -855,84 +855,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>110461</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>165088</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>130168</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>27486</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="正方形/長方形 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A225B2BB-AF70-4BCB-8D27-8B597C3935F7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2591974" y="1187772"/>
-          <a:ext cx="571155" cy="203293"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="accent2"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>105276</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>160420</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>190501</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>150394</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>248151</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>17545</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>59532</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>7519</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -947,13 +879,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3965408" y="671762"/>
-          <a:ext cx="2015290" cy="842211"/>
+          <a:off x="4903495" y="362826"/>
+          <a:ext cx="2002131" cy="853177"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -82773"/>
-            <a:gd name="adj2" fmla="val 27156"/>
+            <a:gd name="adj1" fmla="val -38469"/>
+            <a:gd name="adj2" fmla="val 71115"/>
           </a:avLst>
         </a:prstGeom>
       </xdr:spPr>
@@ -1073,214 +1005,40 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>22622</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>165496</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>195245</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>137228</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05EEBB5B-04C0-4278-AE4D-C414579C68B9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="707231" y="1028699"/>
-          <a:ext cx="8387936" cy="2216060"/>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>169992</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>111510</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>166687</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A225B2BB-AF70-4BCB-8D27-8B597C3935F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4825336" y="1492635"/>
+          <a:ext cx="1092070" cy="227818"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>226218</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>547686</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>172640</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="吹き出し: 四角形 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1917DA5C-DF41-47A3-A70D-61BF5BFE1748}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5018484" y="690563"/>
-          <a:ext cx="3744515" cy="517921"/>
-        </a:xfrm>
-        <a:prstGeom prst="wedgeRectCallout">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val -34142"/>
-            <a:gd name="adj2" fmla="val 75570"/>
-          </a:avLst>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>3.</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>サービスメニューに料金情報管理が存在していること</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>4.</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>サービスメニューの料金情報管理の文字が灰色であること</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>541734</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>41672</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="フローチャート: 処理 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D352E3CB-9652-4B99-A270-56133093383E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4887516" y="1476375"/>
-          <a:ext cx="1131093" cy="291703"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartProcess">
-          <a:avLst/>
-        </a:prstGeom>
         <a:noFill/>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
@@ -1318,27 +1076,27 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>82647</xdr:rowOff>
+      <xdr:colOff>5014</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>5014</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>407391</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>85043</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46A160A4-4E0C-487B-8FD4-DC587B091894}"/>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E46666B6-518B-4EAF-A5B9-16BB7864658B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1347,7 +1105,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1360,8 +1118,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="870857"/>
-          <a:ext cx="10058400" cy="1127676"/>
+          <a:off x="691817" y="1027698"/>
+          <a:ext cx="5896798" cy="2295845"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1372,23 +1130,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>255813</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>326571</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>92528</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>226218</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>547686</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>172640</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="吹き出し: 四角形 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21DB40AF-F89A-46A1-9D9B-1C37BF812047}"/>
+        <xdr:cNvPr id="6" name="吹き出し: 四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1917DA5C-DF41-47A3-A70D-61BF5BFE1748}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1396,13 +1154,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="941613" y="1605642"/>
-          <a:ext cx="2128158" cy="576943"/>
+          <a:off x="5018484" y="690563"/>
+          <a:ext cx="3744515" cy="517921"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 26226"/>
-            <a:gd name="adj2" fmla="val -98982"/>
+            <a:gd name="adj1" fmla="val -34142"/>
+            <a:gd name="adj2" fmla="val 75570"/>
           </a:avLst>
         </a:prstGeom>
       </xdr:spPr>
@@ -1426,6 +1184,298 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>3.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>サービスメニューに料金情報管理が存在していること</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>4.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>サービスメニューの料金情報管理の文字が灰色であること</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>421105</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>180786</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>41672</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="フローチャート: 処理 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D352E3CB-9652-4B99-A270-56133093383E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5228723" y="1458829"/>
+          <a:ext cx="1133287" cy="287317"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>11305</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>145911</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>126577</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>89604</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C34A0D36-CFF9-437B-81FF-DC0D7AE7FF61}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8964805" y="819988"/>
+          <a:ext cx="7002580" cy="5841866"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>473710</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>116914</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A156872F-DE0F-4A52-B30D-2C7D74B2C656}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="688731" y="842596"/>
+          <a:ext cx="8049748" cy="2981741"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>228180</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>11933</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>298938</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>66361</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="吹き出し: 四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21DB40AF-F89A-46A1-9D9B-1C37BF812047}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4360565" y="2034164"/>
+          <a:ext cx="2136950" cy="559985"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 26226"/>
+            <a:gd name="adj2" fmla="val -98982"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
             <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
@@ -1453,56 +1503,6 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>115273</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>117865</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C34A0D36-CFF9-437B-81FF-DC0D7AE7FF61}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="2786743"/>
-          <a:ext cx="6973273" cy="6039693"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2195,23 +2195,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>2359</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>443164</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>130332</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>663464</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>157655</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>515143</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>35860</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3B70238-F4C9-4A9B-A6E7-75C4F345692A}"/>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65027E83-1B39-4CC0-AA24-CC895D48B8EE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2220,7 +2220,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2233,8 +2233,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="683559" y="1515153"/>
-          <a:ext cx="10012987" cy="1136503"/>
+          <a:off x="663464" y="1524000"/>
+          <a:ext cx="8049748" cy="2781688"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2246,15 +2246,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>638674</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>122322</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>170446</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>150395</xdr:rowOff>
+      <xdr:colOff>441605</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>96046</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>656550</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>124119</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2269,13 +2269,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="638674" y="2811734"/>
-          <a:ext cx="2266007" cy="364249"/>
+          <a:off x="441605" y="4536667"/>
+          <a:ext cx="2264462" cy="369659"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 59457"/>
-            <a:gd name="adj2" fmla="val -115489"/>
+            <a:gd name="adj1" fmla="val -3783"/>
+            <a:gd name="adj2" fmla="val -104827"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -2327,15 +2327,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>270709</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>125330</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>15038</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>40106</xdr:rowOff>
+      <xdr:colOff>80210</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>20227</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>507711</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>105795</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2350,13 +2350,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3004944" y="2814742"/>
-          <a:ext cx="2478565" cy="419040"/>
+          <a:off x="2812900" y="4119261"/>
+          <a:ext cx="2477018" cy="427155"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -29082"/>
-            <a:gd name="adj2" fmla="val -103382"/>
+            <a:gd name="adj1" fmla="val -69658"/>
+            <a:gd name="adj2" fmla="val -44944"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -2407,16 +2407,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>464220</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>65172</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>629654</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>63163</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>280289</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>151085</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>445724</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>141991</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2431,13 +2431,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4565573" y="1409878"/>
-          <a:ext cx="2216110" cy="502256"/>
+          <a:off x="3012979" y="2712982"/>
+          <a:ext cx="2214952" cy="503285"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -62725"/>
-            <a:gd name="adj2" fmla="val 123493"/>
+            <a:gd name="adj1" fmla="val -49972"/>
+            <a:gd name="adj2" fmla="val 110622"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -2488,16 +2488,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>196516</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>111293</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>656343</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>12759</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>136359</xdr:rowOff>
+      <xdr:colOff>138605</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>37824</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2512,13 +2512,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="880075" y="1455999"/>
-          <a:ext cx="2216110" cy="697419"/>
+          <a:off x="656343" y="2403862"/>
+          <a:ext cx="2214952" cy="708238"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 51689"/>
-            <a:gd name="adj2" fmla="val 73847"/>
+            <a:gd name="adj1" fmla="val -19785"/>
+            <a:gd name="adj2" fmla="val 84977"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -2570,15 +2570,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>309814</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>1357</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>475248</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>24063</xdr:rowOff>
+      <xdr:colOff>644831</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>21063</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>127093</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>13137</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2593,13 +2593,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5778285" y="2858857"/>
-          <a:ext cx="2216110" cy="695059"/>
+          <a:off x="6110210" y="4120097"/>
+          <a:ext cx="2214952" cy="675247"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -34346"/>
-            <a:gd name="adj2" fmla="val -107713"/>
+            <a:gd name="adj1" fmla="val -26635"/>
+            <a:gd name="adj2" fmla="val -90031"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -2650,23 +2650,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>5443</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>462643</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>128780</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>108232</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>144960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="図 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE172A1B-E52C-4B0C-9285-4219229768B1}"/>
+        <xdr:cNvPr id="19" name="図 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60B9BDBC-7383-441C-8A12-A48DAC19ADBF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2675,7 +2675,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2688,8 +2688,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="692900" y="4174435"/>
-          <a:ext cx="10081591" cy="1172388"/>
+          <a:off x="9610725" y="5676900"/>
+          <a:ext cx="6956707" cy="5955210"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2700,23 +2700,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>98707</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>125910</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>683172</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>170793</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>394680</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>59205</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="図 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60B9BDBC-7383-441C-8A12-A48DAC19ADBF}"/>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AA78F56-0A21-4430-8D73-56A2EC7B947E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2738,8 +2738,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10999304" y="4000500"/>
-          <a:ext cx="6973273" cy="6039693"/>
+          <a:off x="683172" y="5636172"/>
+          <a:ext cx="8592749" cy="2962688"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2755,23 +2755,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>684609</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>473868</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>74540</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>363149</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>48038</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92D8BF11-52C5-44BE-8523-817D7062BF51}"/>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDB31422-C172-4D70-865B-0BAE6F62522C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2793,8 +2793,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="684609" y="863203"/>
-          <a:ext cx="10058400" cy="1628306"/>
+          <a:off x="685800" y="857250"/>
+          <a:ext cx="8592749" cy="2962688"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2805,16 +2805,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>482203</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>166688</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>166688</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>53578</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>606028</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>95251</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2829,8 +2829,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3905250" y="2065735"/>
-          <a:ext cx="369094" cy="232171"/>
+          <a:off x="1291828" y="3181351"/>
+          <a:ext cx="708422" cy="504824"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -2873,16 +2873,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>4647</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>167268</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>266701</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>271347</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>62493</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2897,8 +2897,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4125952" y="2377765"/>
-          <a:ext cx="4646" cy="540137"/>
+          <a:off x="1638301" y="3810000"/>
+          <a:ext cx="4646" cy="538743"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2929,23 +2929,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>416169</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>120254</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>5341</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>148071</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C7C5D3B-615C-41E9-B4B2-7ED0F8A0C772}"/>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63CFBF9E-3DE2-4B30-BDD2-230C4D535E5B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2954,7 +2954,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2967,8 +2967,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="688731" y="2864827"/>
-          <a:ext cx="10058400" cy="1468408"/>
+          <a:off x="8934450" y="4467225"/>
+          <a:ext cx="3415291" cy="4424796"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2977,25 +2977,75 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>391632</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>19459</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67108316-A142-48A6-AA25-F3B1D03927DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="8743950"/>
+          <a:ext cx="7935432" cy="2934109"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>84735</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>105705</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>329033</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>114959</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>357351</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>170892</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>603031</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>25289</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="吹き出し: 四角形 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F41F8918-441F-4AC4-A1F5-B43FCC27A24C}"/>
+        <xdr:cNvPr id="12" name="吹き出し: 四角形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EDD8DD6-8EB3-4D47-AAEA-91AAEAE10C71}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3003,13 +3053,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="765092" y="5058705"/>
-          <a:ext cx="2965727" cy="716825"/>
+          <a:off x="7215351" y="9429192"/>
+          <a:ext cx="2303080" cy="711647"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 33935"/>
-            <a:gd name="adj2" fmla="val -95836"/>
+            <a:gd name="adj1" fmla="val -34481"/>
+            <a:gd name="adj2" fmla="val 86592"/>
           </a:avLst>
         </a:prstGeom>
       </xdr:spPr>
@@ -3033,6 +3083,165 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>料金情報が存在しない場合は</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>該当する情報が見つかりませんでした。</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>と表示される</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>391632</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>86239</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="図 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B73657E-8D7B-48B5-B032-6A74C537B6D7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="4457700"/>
+          <a:ext cx="7935432" cy="3686689"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>284760</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>115230</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>529058</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>124484</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="吹き出し: 四角形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F41F8918-441F-4AC4-A1F5-B43FCC27A24C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5771160" y="5430180"/>
+          <a:ext cx="2987498" cy="695054"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -35251"/>
+            <a:gd name="adj2" fmla="val 94649"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
@@ -3054,25 +3263,30 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>672091</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>138546</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>392464</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>22389</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="図 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63CFBF9E-3DE2-4B30-BDD2-230C4D535E5B}"/>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1297EDB9-03C2-43F9-9B9D-3A2040AD9596}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3081,7 +3295,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3094,8 +3308,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11083636" y="2944091"/>
-          <a:ext cx="3443000" cy="4468091"/>
+          <a:off x="687457" y="4348370"/>
+          <a:ext cx="7954485" cy="3153215"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3104,75 +3318,81 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>488577</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>84956</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="図 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03F2F6A2-067E-4E23-B9AF-A856BC1B0F66}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="683559" y="7563971"/>
-          <a:ext cx="10058400" cy="2102014"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
+      <xdr:colOff>665093</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>111401</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>665750</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>89395</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="直線矢印コネクタ 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B7D6138-011C-469F-A598-9D969769BE14}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1352550" y="3764031"/>
+          <a:ext cx="657" cy="499799"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>462126</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>28017</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>22006</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>53864</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>444363</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>162338</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>225288</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>83654</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="吹き出し: 四角形 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EDD8DD6-8EB3-4D47-AAEA-91AAEAE10C71}"/>
+        <xdr:cNvPr id="10" name="吹き出し: 四角形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EDDBC4E-3877-48B3-B58B-7319FB776DB7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3180,13 +3400,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7320126" y="7057467"/>
-          <a:ext cx="2303080" cy="711647"/>
+          <a:off x="5944015" y="2945295"/>
+          <a:ext cx="2530751" cy="964924"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -34481"/>
-            <a:gd name="adj2" fmla="val 86592"/>
+            <a:gd name="adj1" fmla="val -32865"/>
+            <a:gd name="adj2" fmla="val 80723"/>
           </a:avLst>
         </a:prstGeom>
       </xdr:spPr>
@@ -3210,7 +3430,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -3219,10 +3439,10 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>料金情報が存在しない場合は</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+            <a:t>14.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -3231,7 +3451,134 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>”</a:t>
+            <a:t>「料金名」に”通常”と入力して検索ボタンを押下したときに、検索結果画面に遷移し”通常”と部分一致した料金名を持つ料金情報が表示される</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>8283</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>33129</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>351234</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>37593</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D267CBBF-0A8C-4C97-BCDD-FDD5A1D7906B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8908205" y="4349145"/>
+          <a:ext cx="3765998" cy="4838401"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>387362</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>169886</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>251698</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>46370</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="吹き出し: 四角形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDCF51C2-A313-4A26-BF7B-1BE8943E8CB0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5179628" y="11218886"/>
+          <a:ext cx="3287383" cy="739687"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -34008"/>
+            <a:gd name="adj2" fmla="val 94630"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>15.</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
@@ -3239,7 +3586,31 @@
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
               <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>入力した文字と部分一致する料金情報が存在しない場合は</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-ea"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
@@ -3248,26 +3619,28 @@
           <a:r>
             <a:rPr lang="en-US" altLang="ja-JP">
               <a:effectLst/>
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
             </a:rPr>
             <a:t>”</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP">
               <a:effectLst/>
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
             </a:rPr>
             <a:t>と表示される</a:t>
           </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="+mn-ea"/>
+            <a:ea typeface="+mn-ea"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -3276,17 +3649,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>258934</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>166955</xdr:rowOff>
+      <xdr:rowOff>65417</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DD5BAB5-BDC8-4D79-AD7B-E062BA2E8A2B}"/>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF0427FC-31D9-48A9-A3AE-E2C016C46E20}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3295,7 +3668,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3308,8 +3681,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="857250"/>
-          <a:ext cx="10058400" cy="2910155"/>
+          <a:off x="687457" y="869674"/>
+          <a:ext cx="3696216" cy="2848373"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3320,16 +3693,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>296517</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>125481</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>344142</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>37272</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3344,8 +3717,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6477000" y="3095625"/>
-          <a:ext cx="733425" cy="428625"/>
+          <a:off x="983974" y="3256307"/>
+          <a:ext cx="735081" cy="433595"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -3386,25 +3759,143 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>252562</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>91290</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37E94338-9E59-4FF5-A1F3-743F72DFC298}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="688731" y="8763000"/>
+          <a:ext cx="3696216" cy="3124636"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>19707</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>6569</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>241789</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>21981</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>289414</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>102291</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="フローチャート: 処理 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78AAB5C6-C990-468B-AA40-0BFCCAEA16A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="930520" y="11144250"/>
+          <a:ext cx="736356" cy="417349"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>586154</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>586811</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>146515</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="6" name="直線矢印コネクタ 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B7D6138-011C-469F-A598-9D969769BE14}"/>
+        <xdr:cNvPr id="21" name="直線矢印コネクタ 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D613165C-64A4-4961-8E1F-A171E8F7968D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3412,8 +3903,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6850774" y="3615230"/>
-          <a:ext cx="657" cy="490373"/>
+          <a:off x="1274885" y="11627828"/>
+          <a:ext cx="657" cy="483552"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3446,21 +3937,126 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>36536</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>311763</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>141877</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FD5FA7C-72AF-4C24-BEDA-A64B90DB5469}"/>
+        <xdr:cNvPr id="23" name="図 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF124211-DDBA-45E3-AA21-44AC22743B7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="688731" y="12133385"/>
+          <a:ext cx="7887801" cy="3343742"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>373411</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>34058</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7E26A53-2A23-4B02-A1FC-AC4329E109C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="687457" y="2261152"/>
+          <a:ext cx="7935432" cy="3686689"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>616</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>161351</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>101203</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>162249</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36AC82E2-7B47-43A8-AFCB-F76625FBCA69}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3482,8 +4078,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="4114800"/>
-          <a:ext cx="10058400" cy="1579586"/>
+          <a:off x="8900538" y="2233039"/>
+          <a:ext cx="3523634" cy="4489554"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3494,23 +4090,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>567059</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>46897</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>79628</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>161368</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="吹き出し: 四角形 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EDDBC4E-3877-48B3-B58B-7319FB776DB7}"/>
+        <xdr:cNvPr id="6" name="吹き出し: 四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02159C1E-B3E2-4A86-9500-072ED2D69A64}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3518,13 +4114,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5972175" y="6038850"/>
-          <a:ext cx="2524125" cy="952500"/>
+          <a:off x="1933404" y="5683069"/>
+          <a:ext cx="2245258" cy="456058"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -22719"/>
-            <a:gd name="adj2" fmla="val -75500"/>
+            <a:gd name="adj1" fmla="val -74483"/>
+            <a:gd name="adj2" fmla="val -98269"/>
           </a:avLst>
         </a:prstGeom>
       </xdr:spPr>
@@ -3548,7 +4144,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -3557,22 +4153,10 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>14.</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>「料金名」に”通常”と入力して検索ボタンを押下したときに、検索結果画面に遷移し”通常”と部分一致した料金名を持つ料金情報が表示される</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>24.料金番号欄にある番号がリンクになっていること</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
             <a:t> </a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
@@ -3581,125 +4165,25 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>2</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>611043</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>161192</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D267CBBF-0A8C-4C97-BCDD-FDD5A1D7906B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11019694" y="4044462"/>
-          <a:ext cx="3365964" cy="4205653"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>44614</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="図 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D27A600C-E1C7-494E-BB09-6EBC1453214C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="8915400"/>
-          <a:ext cx="10058400" cy="2102014"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>512379</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>86541</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>376715</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>135665</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>35428</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>105103</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>235455</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>113387</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="吹き出し: 四角形 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDCF51C2-A313-4A26-BF7B-1BE8943E8CB0}"/>
+        <xdr:cNvPr id="7" name="吹き出し: 四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4410043D-A708-43C6-9A5B-07F171B47ECF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3707,13 +4191,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7386944" y="7913606"/>
-          <a:ext cx="3301619" cy="744863"/>
+          <a:off x="35428" y="3520965"/>
+          <a:ext cx="2249544" cy="349870"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -34008"/>
-            <a:gd name="adj2" fmla="val 94630"/>
+            <a:gd name="adj1" fmla="val -9149"/>
+            <a:gd name="adj2" fmla="val 101288"/>
           </a:avLst>
         </a:prstGeom>
       </xdr:spPr>
@@ -3737,316 +4221,6 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-ea"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>15.</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-ea"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>入力した文字と部分一致する料金情報が存在しない場合は</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-ea"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>”</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-ea"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>該当する情報が見つかりませんでした。</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP">
-              <a:effectLst/>
-              <a:latin typeface="+mn-ea"/>
-              <a:ea typeface="+mn-ea"/>
-            </a:rPr>
-            <a:t>”</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="ja-JP">
-              <a:effectLst/>
-              <a:latin typeface="+mn-ea"/>
-              <a:ea typeface="+mn-ea"/>
-            </a:rPr>
-            <a:t>と表示される</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-            <a:latin typeface="+mn-ea"/>
-            <a:ea typeface="+mn-ea"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>443164</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>122705</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2684C9D8-F02E-4499-9FC2-3961B0F4CB65}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="686803" y="2215816"/>
-          <a:ext cx="10058400" cy="1997626"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>501512</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>157370</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36AC82E2-7B47-43A8-AFCB-F76625FBCA69}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10999304" y="2261153"/>
-          <a:ext cx="3251338" cy="4157869"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>215762</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>14908</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>415787</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>132522</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="吹き出し: 四角形 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02159C1E-B3E2-4A86-9500-072ED2D69A64}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2965588" y="4363278"/>
-          <a:ext cx="2262395" cy="465483"/>
-        </a:xfrm>
-        <a:prstGeom prst="wedgeRectCallout">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val -21565"/>
-            <a:gd name="adj2" fmla="val -90981"/>
-          </a:avLst>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>24.料金番号欄にある番号がリンクになっていること</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="ja-JP"/>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>442705</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>642731</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>8284</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="吹き出し: 四角形 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4410043D-A708-43C6-9A5B-07F171B47ECF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1130162" y="3130826"/>
-          <a:ext cx="2262395" cy="356154"/>
-        </a:xfrm>
-        <a:prstGeom prst="wedgeRectCallout">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 54217"/>
-            <a:gd name="adj2" fmla="val 29942"/>
-          </a:avLst>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
@@ -4070,16 +4244,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>626451</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>166623</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>124810</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>650327</xdr:colOff>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>131379</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>426982</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>84992</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4094,13 +4268,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4042313" y="1326931"/>
-          <a:ext cx="2533221" cy="807578"/>
+          <a:off x="4948830" y="1149569"/>
+          <a:ext cx="2533221" cy="860534"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -60280"/>
-            <a:gd name="adj2" fmla="val 87432"/>
+            <a:gd name="adj1" fmla="val -20864"/>
+            <a:gd name="adj2" fmla="val 117966"/>
           </a:avLst>
         </a:prstGeom>
       </xdr:spPr>
@@ -4197,16 +4371,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>404675</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>150024</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>273295</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>104042</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>102578</xdr:rowOff>
+      <xdr:colOff>607630</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>148560</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4221,13 +4395,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8538064" y="4148504"/>
-          <a:ext cx="2269148" cy="335574"/>
+          <a:off x="6553227" y="5615403"/>
+          <a:ext cx="2252472" cy="340123"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 155"/>
-            <a:gd name="adj2" fmla="val -194527"/>
+            <a:gd name="adj1" fmla="val 154"/>
+            <a:gd name="adj2" fmla="val -296889"/>
           </a:avLst>
         </a:prstGeom>
       </xdr:spPr>
@@ -4274,16 +4448,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>25897</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>112935</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>91587</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>139211</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>291611</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>7327</xdr:rowOff>
+      <xdr:colOff>225921</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>151844</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4298,13 +4472,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8356356" y="2835519"/>
-          <a:ext cx="2266217" cy="373673"/>
+          <a:off x="6174449" y="3870383"/>
+          <a:ext cx="2249541" cy="380495"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -67713"/>
-            <a:gd name="adj2" fmla="val 109559"/>
+            <a:gd name="adj1" fmla="val -55740"/>
+            <a:gd name="adj2" fmla="val 123370"/>
           </a:avLst>
         </a:prstGeom>
       </xdr:spPr>
@@ -4351,16 +4525,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>139210</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>608135</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>153865</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>160612</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>126073</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>568722</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>140728</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4375,8 +4549,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6398602" y="2835518"/>
-          <a:ext cx="1785571" cy="351693"/>
+          <a:off x="4259646" y="3883521"/>
+          <a:ext cx="1774455" cy="356241"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
@@ -4428,16 +4602,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>462330</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>137745</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>36636</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>146538</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>232416</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>164021</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>489895</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>2020</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4452,8 +4626,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4594715" y="3002572"/>
-          <a:ext cx="1640498" cy="345831"/>
+          <a:off x="2281933" y="4092262"/>
+          <a:ext cx="1623824" cy="350379"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst/>
@@ -4502,16 +4676,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>13138</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>123155</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>175254</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>159998</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>587111</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>116036</xdr:rowOff>
+      <xdr:colOff>424995</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>79193</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4526,13 +4700,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1544473" y="3785451"/>
-          <a:ext cx="1781076" cy="301319"/>
+          <a:off x="13138" y="5759327"/>
+          <a:ext cx="1778202" cy="297625"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 60466"/>
-            <a:gd name="adj2" fmla="val -108870"/>
+            <a:gd name="adj1" fmla="val -3512"/>
+            <a:gd name="adj2" fmla="val -188058"/>
           </a:avLst>
         </a:prstGeom>
       </xdr:spPr>
@@ -5013,21 +5187,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA6086F6-0F8A-4A4A-BA94-FB8F737A2B82}">
-  <dimension ref="B2:B15"/>
+  <dimension ref="B2:N4"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B15" t="s">
+      <c r="N4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -5072,7 +5244,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3015BBAC-5FAC-4596-B4D4-81A1282635D4}">
-  <dimension ref="B2:Q23"/>
+  <dimension ref="B2:O32"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
@@ -5105,11 +5277,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
-      <c r="B23" t="s">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B32" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="O32" t="s">
         <v>22</v>
       </c>
     </row>
@@ -5123,7 +5295,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F923521-FC7B-4494-925D-1FA7461D059B}">
-  <dimension ref="B2:Q44"/>
+  <dimension ref="B2:N50"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
@@ -5136,16 +5308,16 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.15">
-      <c r="Q17" t="s">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="B21" s="3"/>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.15">
+      <c r="N25" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
-      <c r="B21" s="3"/>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B44" s="3" t="s">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B50" s="3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -5158,7 +5330,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{737BB949-CBBA-4DBD-A3DA-7D897858559F}">
-  <dimension ref="B2:Q51"/>
+  <dimension ref="B2:N51"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
@@ -5171,8 +5343,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="17:17" x14ac:dyDescent="0.15">
-      <c r="Q24" t="s">
+    <row r="24" spans="14:14" x14ac:dyDescent="0.15">
+      <c r="N24" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5190,61 +5362,59 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58E1C66B-2D92-443B-BB65-EE856175325E}">
-  <dimension ref="B2:Q13"/>
+  <dimension ref="B2:N12"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B6" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B9" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B10" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.15">
       <c r="B12" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.15">
-      <c r="Q13" t="s">
+      <c r="N12" t="s">
         <v>11</v>
       </c>
     </row>
@@ -5256,18 +5426,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5429,6 +5599,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8048152-0CA9-47E5-A6CC-6D3980A2E781}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -5440,14 +5618,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="dab87824-9c6b-4a08-9c96-9c9ea904f12c"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
